--- a/diseases/d242/2005-2009.xlsx
+++ b/diseases/d242/2005-2009.xlsx
@@ -3216,11 +3216,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_LGV_ANNUAL</t>
@@ -3238,12 +3233,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3253,11 +3243,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3323,17 +3308,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3358,12 +3343,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3372,34 +3357,12 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3407,64 +3370,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN20" t="b">
-        <v>1</v>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3472,27 +3377,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
         <v>1</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -3500,7 +3395,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3520,7 +3415,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -3562,12 +3457,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3601,17 +3496,17 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.292954070111599</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3631,7 +3526,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
@@ -3644,7 +3539,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3664,7 +3559,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -3706,12 +3601,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3745,17 +3640,17 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.292954070111599</v>
+        <v>0</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3775,7 +3670,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -3783,42 +3678,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3745,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3889,17 +3784,17 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.2795118413444637</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3919,7 +3814,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -3927,42 +3822,42 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3889,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4033,17 +3928,17 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2795118413444637</v>
+        <v>0</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4063,7 +3958,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -4076,7 +3971,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -4096,7 +3991,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4138,12 +4033,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4177,17 +4072,17 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.04552165886387499</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4207,7 +4102,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4215,42 +4110,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4177,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4321,17 +4216,17 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.04552165886387499</v>
+        <v>0</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4351,7 +4246,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -4359,42 +4254,42 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4321,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4465,17 +4360,17 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.423437712947582</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4495,7 +4390,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -4508,7 +4403,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4528,7 +4423,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4570,12 +4465,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4609,17 +4504,17 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.423437712947582</v>
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4639,7 +4534,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -4647,42 +4542,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4609,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4763,7 +4658,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4783,7 +4678,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -4791,42 +4686,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4753,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4888,31 +4783,26 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.1120478780582943</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4927,27 +4817,17 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -4955,7 +4835,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4975,7 +4855,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -5012,17 +4892,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5047,12 +4927,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5061,34 +4941,12 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5096,64 +4954,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
-        <v>1</v>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5161,27 +4961,17 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
         <v>1</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -5189,7 +4979,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -5209,7 +4999,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -5251,12 +5041,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5290,17 +5080,17 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1120478780582943</v>
+        <v>0.5278712853219837</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5320,7 +5110,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -5333,7 +5123,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5353,7 +5143,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5395,12 +5185,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5444,7 +5234,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5464,7 +5254,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -5477,7 +5267,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5497,7 +5287,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5539,12 +5329,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5578,17 +5368,17 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5278712853219837</v>
+        <v>0</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5608,7 +5398,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5616,42 +5406,42 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5683,12 +5473,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5722,17 +5512,17 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.3014801231131969</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5752,7 +5542,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -5765,7 +5555,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -5785,7 +5575,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -5827,12 +5617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5876,7 +5666,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5896,7 +5686,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -5904,42 +5694,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5761,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6010,17 +5800,17 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3014801231131969</v>
+        <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -6040,7 +5830,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -6048,42 +5838,42 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -6115,12 +5905,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6154,17 +5944,17 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.006715726842108762</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6184,7 +5974,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -6197,7 +5987,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6217,7 +6007,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6259,12 +6049,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6308,7 +6098,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6328,7 +6118,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6336,42 +6126,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6193,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6442,17 +6232,17 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.006715726842108762</v>
+        <v>0</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6472,7 +6262,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6485,7 +6275,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6505,7 +6295,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6547,12 +6337,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6586,17 +6376,17 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.6025091614530543</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6616,7 +6406,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -6629,7 +6419,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -6649,7 +6439,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -6691,12 +6481,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6740,7 +6530,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6760,7 +6550,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6768,42 +6558,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6835,12 +6625,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6874,17 +6664,17 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.6025091614530543</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6904,7 +6694,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -6917,7 +6707,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6937,7 +6727,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6979,12 +6769,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7009,26 +6799,26 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.1572191011404812</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -7048,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -7056,42 +6846,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7123,12 +6913,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7153,12 +6943,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7170,14 +6960,9 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7192,27 +6977,17 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
         <v>1</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -7220,7 +6995,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -7240,7 +7015,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -7277,17 +7052,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7312,12 +7087,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7326,34 +7101,12 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7361,64 +7114,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN46" t="b">
-        <v>1</v>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7426,27 +7121,17 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
         <v>1</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -7454,7 +7139,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -7474,7 +7159,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -7516,12 +7201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7555,17 +7240,17 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1572191011404812</v>
+        <v>0.3802162271578312</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7585,7 +7270,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -7598,7 +7283,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -7618,7 +7303,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -7660,12 +7345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7709,7 +7394,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7729,7 +7414,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -7742,7 +7427,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -7762,7 +7447,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -7804,12 +7489,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7853,7 +7538,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7873,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7881,42 +7566,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7633,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7987,17 +7672,17 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="O50" t="n">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3802162271578312</v>
+        <v>0.2479752996763498</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -8017,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -8030,7 +7715,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -8050,7 +7735,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -8092,12 +7777,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8141,7 +7826,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -8161,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -8174,7 +7859,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -8194,7 +7879,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -8236,12 +7921,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8285,7 +7970,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -8305,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8313,42 +7998,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8065,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8419,17 +8104,17 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2479752996763498</v>
+        <v>0.01335469851388331</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8449,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8462,7 +8147,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -8482,7 +8167,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -8524,12 +8209,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8573,7 +8258,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8593,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8606,7 +8291,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -8626,7 +8311,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -8668,12 +8353,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8717,7 +8402,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8737,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8745,42 +8430,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8497,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8851,17 +8536,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01335469851388331</v>
+        <v>0</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8881,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8894,7 +8579,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -8914,7 +8599,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -8956,12 +8641,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8995,17 +8680,17 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>0.5154592832119106</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -9025,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -9038,7 +8723,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -9058,7 +8743,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -9100,12 +8785,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9149,7 +8834,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -9169,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -9182,7 +8867,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -9202,7 +8887,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -9244,12 +8929,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9293,7 +8978,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -9313,7 +8998,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9321,42 +9006,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9073,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9427,17 +9112,17 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.5154592832119106</v>
+        <v>0</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9457,7 +9142,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9470,7 +9155,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -9490,7 +9175,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -9499,687 +9184,6 @@
         </is>
       </c>
       <c r="BC60" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP61" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV61" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA61" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB61" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC61" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV62" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Sweden Public Health Agency SmiNet</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>official_html_csv</t>
-        </is>
-      </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>Sweden Public Health Agency SmiNet</t>
-        </is>
-      </c>
-      <c r="BB62" t="inlineStr">
-        <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
-        </is>
-      </c>
-      <c r="BC62" t="inlineStr">
-        <is>
-          <t>official_html_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV63" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA63" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB63" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC63" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV64" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA64" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB64" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC64" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -10311,7 +9315,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -10331,7 +9335,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -10341,7 +9345,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
